--- a/input/reg_health_wellbeing.xlsx
+++ b/input/reg_health_wellbeing.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="504" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1008" uniqueCount="77">
   <si>
     <t>c1</t>
   </si>
@@ -258,7 +258,1351 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="337">
+  <fonts count="673">
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
@@ -1616,7 +2960,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="337">
+  <borders count="673">
     <border>
       <left/>
       <right/>
@@ -3976,11 +5320,2363 @@
       <bottom style="none"/>
       <diagonal style="none"/>
     </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="337">
+  <cellXfs count="673">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="2" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
@@ -5323,6 +9019,1350 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="2" fontId="336" fillId="0" borderId="336" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="337" fillId="0" borderId="337" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="338" fillId="0" borderId="338" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="339" fillId="0" borderId="339" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="340" fillId="0" borderId="340" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="341" fillId="0" borderId="341" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="342" fillId="0" borderId="342" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="343" fillId="0" borderId="343" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="344" fillId="0" borderId="344" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="345" fillId="0" borderId="345" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="346" fillId="0" borderId="346" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="347" fillId="0" borderId="347" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="348" fillId="0" borderId="348" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="349" fillId="0" borderId="349" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="350" fillId="0" borderId="350" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="351" fillId="0" borderId="351" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="352" fillId="0" borderId="352" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="353" fillId="0" borderId="353" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="354" fillId="0" borderId="354" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="355" fillId="0" borderId="355" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="356" fillId="0" borderId="356" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="357" fillId="0" borderId="357" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="358" fillId="0" borderId="358" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="359" fillId="0" borderId="359" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="360" fillId="0" borderId="360" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="361" fillId="0" borderId="361" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="362" fillId="0" borderId="362" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="363" fillId="0" borderId="363" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="364" fillId="0" borderId="364" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="365" fillId="0" borderId="365" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="366" fillId="0" borderId="366" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="367" fillId="0" borderId="367" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="368" fillId="0" borderId="368" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="369" fillId="0" borderId="369" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="370" fillId="0" borderId="370" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="371" fillId="0" borderId="371" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="372" fillId="0" borderId="372" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="373" fillId="0" borderId="373" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="374" fillId="0" borderId="374" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="375" fillId="0" borderId="375" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="376" fillId="0" borderId="376" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="377" fillId="0" borderId="377" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="378" fillId="0" borderId="378" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="379" fillId="0" borderId="379" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="380" fillId="0" borderId="380" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="381" fillId="0" borderId="381" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="382" fillId="0" borderId="382" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="383" fillId="0" borderId="383" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="384" fillId="0" borderId="384" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="385" fillId="0" borderId="385" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="386" fillId="0" borderId="386" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="387" fillId="0" borderId="387" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="388" fillId="0" borderId="388" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="389" fillId="0" borderId="389" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="390" fillId="0" borderId="390" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="391" fillId="0" borderId="391" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="392" fillId="0" borderId="392" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="393" fillId="0" borderId="393" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="394" fillId="0" borderId="394" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="395" fillId="0" borderId="395" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="396" fillId="0" borderId="396" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="397" fillId="0" borderId="397" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="398" fillId="0" borderId="398" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="399" fillId="0" borderId="399" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="400" fillId="0" borderId="400" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="401" fillId="0" borderId="401" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="402" fillId="0" borderId="402" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="403" fillId="0" borderId="403" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="404" fillId="0" borderId="404" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="405" fillId="0" borderId="405" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="406" fillId="0" borderId="406" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="407" fillId="0" borderId="407" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="408" fillId="0" borderId="408" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="409" fillId="0" borderId="409" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="410" fillId="0" borderId="410" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="411" fillId="0" borderId="411" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="412" fillId="0" borderId="412" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="413" fillId="0" borderId="413" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="414" fillId="0" borderId="414" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="415" fillId="0" borderId="415" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="416" fillId="0" borderId="416" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="417" fillId="0" borderId="417" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="418" fillId="0" borderId="418" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="419" fillId="0" borderId="419" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="420" fillId="0" borderId="420" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="421" fillId="0" borderId="421" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="422" fillId="0" borderId="422" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="423" fillId="0" borderId="423" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="424" fillId="0" borderId="424" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="425" fillId="0" borderId="425" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="426" fillId="0" borderId="426" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="427" fillId="0" borderId="427" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="428" fillId="0" borderId="428" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="429" fillId="0" borderId="429" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="430" fillId="0" borderId="430" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="431" fillId="0" borderId="431" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="432" fillId="0" borderId="432" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="433" fillId="0" borderId="433" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="434" fillId="0" borderId="434" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="435" fillId="0" borderId="435" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="436" fillId="0" borderId="436" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="437" fillId="0" borderId="437" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="438" fillId="0" borderId="438" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="439" fillId="0" borderId="439" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="440" fillId="0" borderId="440" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="441" fillId="0" borderId="441" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="442" fillId="0" borderId="442" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="443" fillId="0" borderId="443" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="444" fillId="0" borderId="444" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="445" fillId="0" borderId="445" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="446" fillId="0" borderId="446" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="447" fillId="0" borderId="447" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="448" fillId="0" borderId="448" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="449" fillId="0" borderId="449" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="450" fillId="0" borderId="450" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="451" fillId="0" borderId="451" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="452" fillId="0" borderId="452" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="453" fillId="0" borderId="453" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="454" fillId="0" borderId="454" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="455" fillId="0" borderId="455" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="456" fillId="0" borderId="456" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="457" fillId="0" borderId="457" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="458" fillId="0" borderId="458" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="459" fillId="0" borderId="459" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="460" fillId="0" borderId="460" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="461" fillId="0" borderId="461" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="462" fillId="0" borderId="462" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="463" fillId="0" borderId="463" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="464" fillId="0" borderId="464" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="465" fillId="0" borderId="465" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="466" fillId="0" borderId="466" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="467" fillId="0" borderId="467" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="468" fillId="0" borderId="468" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="469" fillId="0" borderId="469" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="470" fillId="0" borderId="470" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="471" fillId="0" borderId="471" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="472" fillId="0" borderId="472" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="473" fillId="0" borderId="473" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="474" fillId="0" borderId="474" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="475" fillId="0" borderId="475" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="476" fillId="0" borderId="476" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="477" fillId="0" borderId="477" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="478" fillId="0" borderId="478" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="479" fillId="0" borderId="479" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="480" fillId="0" borderId="480" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="481" fillId="0" borderId="481" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="482" fillId="0" borderId="482" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="483" fillId="0" borderId="483" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="484" fillId="0" borderId="484" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="485" fillId="0" borderId="485" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="486" fillId="0" borderId="486" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="487" fillId="0" borderId="487" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="488" fillId="0" borderId="488" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="489" fillId="0" borderId="489" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="490" fillId="0" borderId="490" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="491" fillId="0" borderId="491" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="492" fillId="0" borderId="492" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="493" fillId="0" borderId="493" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="494" fillId="0" borderId="494" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="495" fillId="0" borderId="495" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="496" fillId="0" borderId="496" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="497" fillId="0" borderId="497" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="498" fillId="0" borderId="498" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="499" fillId="0" borderId="499" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="500" fillId="0" borderId="500" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="501" fillId="0" borderId="501" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="502" fillId="0" borderId="502" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="503" fillId="0" borderId="503" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="504" fillId="0" borderId="504" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="505" fillId="0" borderId="505" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="506" fillId="0" borderId="506" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="507" fillId="0" borderId="507" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="508" fillId="0" borderId="508" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="509" fillId="0" borderId="509" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="510" fillId="0" borderId="510" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="511" fillId="0" borderId="511" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="512" fillId="0" borderId="512" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="513" fillId="0" borderId="513" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="514" fillId="0" borderId="514" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="515" fillId="0" borderId="515" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="516" fillId="0" borderId="516" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="517" fillId="0" borderId="517" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="518" fillId="0" borderId="518" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="519" fillId="0" borderId="519" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="520" fillId="0" borderId="520" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="521" fillId="0" borderId="521" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="522" fillId="0" borderId="522" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="523" fillId="0" borderId="523" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="524" fillId="0" borderId="524" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="525" fillId="0" borderId="525" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="526" fillId="0" borderId="526" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="527" fillId="0" borderId="527" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="528" fillId="0" borderId="528" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="529" fillId="0" borderId="529" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="530" fillId="0" borderId="530" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="531" fillId="0" borderId="531" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="532" fillId="0" borderId="532" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="533" fillId="0" borderId="533" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="534" fillId="0" borderId="534" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="535" fillId="0" borderId="535" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="536" fillId="0" borderId="536" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="537" fillId="0" borderId="537" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="538" fillId="0" borderId="538" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="539" fillId="0" borderId="539" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="540" fillId="0" borderId="540" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="541" fillId="0" borderId="541" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="542" fillId="0" borderId="542" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="543" fillId="0" borderId="543" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="544" fillId="0" borderId="544" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="545" fillId="0" borderId="545" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="546" fillId="0" borderId="546" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="547" fillId="0" borderId="547" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="548" fillId="0" borderId="548" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="549" fillId="0" borderId="549" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="550" fillId="0" borderId="550" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="551" fillId="0" borderId="551" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="552" fillId="0" borderId="552" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="553" fillId="0" borderId="553" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="554" fillId="0" borderId="554" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="555" fillId="0" borderId="555" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="556" fillId="0" borderId="556" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="557" fillId="0" borderId="557" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="558" fillId="0" borderId="558" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="559" fillId="0" borderId="559" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="560" fillId="0" borderId="560" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="561" fillId="0" borderId="561" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="562" fillId="0" borderId="562" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="563" fillId="0" borderId="563" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="564" fillId="0" borderId="564" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="565" fillId="0" borderId="565" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="566" fillId="0" borderId="566" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="567" fillId="0" borderId="567" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="568" fillId="0" borderId="568" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="569" fillId="0" borderId="569" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="570" fillId="0" borderId="570" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="571" fillId="0" borderId="571" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="572" fillId="0" borderId="572" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="573" fillId="0" borderId="573" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="574" fillId="0" borderId="574" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="575" fillId="0" borderId="575" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="576" fillId="0" borderId="576" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="577" fillId="0" borderId="577" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="578" fillId="0" borderId="578" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="579" fillId="0" borderId="579" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="580" fillId="0" borderId="580" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="581" fillId="0" borderId="581" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="582" fillId="0" borderId="582" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="583" fillId="0" borderId="583" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="584" fillId="0" borderId="584" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="585" fillId="0" borderId="585" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="586" fillId="0" borderId="586" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="587" fillId="0" borderId="587" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="588" fillId="0" borderId="588" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="589" fillId="0" borderId="589" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="590" fillId="0" borderId="590" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="591" fillId="0" borderId="591" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="592" fillId="0" borderId="592" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="593" fillId="0" borderId="593" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="594" fillId="0" borderId="594" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="595" fillId="0" borderId="595" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="596" fillId="0" borderId="596" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="597" fillId="0" borderId="597" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="598" fillId="0" borderId="598" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="599" fillId="0" borderId="599" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="600" fillId="0" borderId="600" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="601" fillId="0" borderId="601" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="602" fillId="0" borderId="602" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="603" fillId="0" borderId="603" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="604" fillId="0" borderId="604" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="605" fillId="0" borderId="605" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="606" fillId="0" borderId="606" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="607" fillId="0" borderId="607" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="608" fillId="0" borderId="608" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="609" fillId="0" borderId="609" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="610" fillId="0" borderId="610" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="611" fillId="0" borderId="611" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="612" fillId="0" borderId="612" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="613" fillId="0" borderId="613" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="614" fillId="0" borderId="614" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="615" fillId="0" borderId="615" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="616" fillId="0" borderId="616" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="617" fillId="0" borderId="617" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="618" fillId="0" borderId="618" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="619" fillId="0" borderId="619" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="620" fillId="0" borderId="620" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="621" fillId="0" borderId="621" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="622" fillId="0" borderId="622" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="623" fillId="0" borderId="623" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="624" fillId="0" borderId="624" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="625" fillId="0" borderId="625" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="626" fillId="0" borderId="626" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="627" fillId="0" borderId="627" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="628" fillId="0" borderId="628" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="629" fillId="0" borderId="629" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="630" fillId="0" borderId="630" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="631" fillId="0" borderId="631" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="632" fillId="0" borderId="632" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="633" fillId="0" borderId="633" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="634" fillId="0" borderId="634" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="635" fillId="0" borderId="635" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="636" fillId="0" borderId="636" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="637" fillId="0" borderId="637" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="638" fillId="0" borderId="638" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="639" fillId="0" borderId="639" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="640" fillId="0" borderId="640" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="641" fillId="0" borderId="641" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="642" fillId="0" borderId="642" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="643" fillId="0" borderId="643" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="644" fillId="0" borderId="644" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="645" fillId="0" borderId="645" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="646" fillId="0" borderId="646" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="647" fillId="0" borderId="647" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="648" fillId="0" borderId="648" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="649" fillId="0" borderId="649" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="650" fillId="0" borderId="650" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="651" fillId="0" borderId="651" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="652" fillId="0" borderId="652" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="653" fillId="0" borderId="653" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="654" fillId="0" borderId="654" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="655" fillId="0" borderId="655" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="656" fillId="0" borderId="656" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="657" fillId="0" borderId="657" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="658" fillId="0" borderId="658" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="659" fillId="0" borderId="659" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="660" fillId="0" borderId="660" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="661" fillId="0" borderId="661" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="662" fillId="0" borderId="662" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="663" fillId="0" borderId="663" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="664" fillId="0" borderId="664" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="665" fillId="0" borderId="665" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="666" fillId="0" borderId="666" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="667" fillId="0" borderId="667" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="668" fillId="0" borderId="668" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="669" fillId="0" borderId="669" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="670" fillId="0" borderId="670" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="671" fillId="0" borderId="671" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="672" fillId="0" borderId="672" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -5339,10 +10379,10 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="337" t="s">
         <v>32</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="338" t="s">
         <v>64</v>
       </c>
       <c r="C1" t="s">
@@ -5440,10 +10480,10 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="s">
+      <c r="A2" s="339" t="s">
         <v>33</v>
       </c>
-      <c r="B2" s="4">
+      <c r="B2" s="340">
         <v>0.5510632799676517</v>
       </c>
       <c r="C2">
@@ -5541,10 +10581,10 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="5" t="s">
+      <c r="A3" s="341" t="s">
         <v>34</v>
       </c>
-      <c r="B3" s="6">
+      <c r="B3" s="342">
         <v>-0.32776165442113886</v>
       </c>
       <c r="C3">
@@ -5642,10 +10682,10 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="7" t="s">
+      <c r="A4" s="343" t="s">
         <v>35</v>
       </c>
-      <c r="B4" s="8">
+      <c r="B4" s="344">
         <v>-0.026533928728183491</v>
       </c>
       <c r="C4">
@@ -5743,10 +10783,10 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="9" t="s">
+      <c r="A5" s="345" t="s">
         <v>36</v>
       </c>
-      <c r="B5" s="10">
+      <c r="B5" s="346">
         <v>0.10897131759989309</v>
       </c>
       <c r="C5">
@@ -5844,10 +10884,10 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="11" t="s">
+      <c r="A6" s="347" t="s">
         <v>37</v>
       </c>
-      <c r="B6" s="12">
+      <c r="B6" s="348">
         <v>-0.017969641016080853</v>
       </c>
       <c r="C6">
@@ -5945,10 +10985,10 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="13" t="s">
+      <c r="A7" s="349" t="s">
         <v>38</v>
       </c>
-      <c r="B7" s="14">
+      <c r="B7" s="350">
         <v>0.027711399258668848</v>
       </c>
       <c r="C7">
@@ -6046,10 +11086,10 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="15" t="s">
+      <c r="A8" s="351" t="s">
         <v>39</v>
       </c>
-      <c r="B8" s="16">
+      <c r="B8" s="352">
         <v>0.10981611257005139</v>
       </c>
       <c r="C8">
@@ -6147,10 +11187,10 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="17" t="s">
+      <c r="A9" s="353" t="s">
         <v>40</v>
       </c>
-      <c r="B9" s="18">
+      <c r="B9" s="354">
         <v>0.16876210295288158</v>
       </c>
       <c r="C9">
@@ -6248,10 +11288,10 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="19" t="s">
+      <c r="A10" s="355" t="s">
         <v>41</v>
       </c>
-      <c r="B10" s="20">
+      <c r="B10" s="356">
         <v>-0.15488580932884538</v>
       </c>
       <c r="C10">
@@ -6349,10 +11389,10 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="21" t="s">
+      <c r="A11" s="357" t="s">
         <v>42</v>
       </c>
-      <c r="B11" s="22">
+      <c r="B11" s="358">
         <v>0.14159240454775313</v>
       </c>
       <c r="C11">
@@ -6450,10 +11490,10 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="23" t="s">
+      <c r="A12" s="359" t="s">
         <v>43</v>
       </c>
-      <c r="B12" s="24">
+      <c r="B12" s="360">
         <v>0.044677115561424147</v>
       </c>
       <c r="C12">
@@ -6551,10 +11591,10 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="25" t="s">
+      <c r="A13" s="361" t="s">
         <v>44</v>
       </c>
-      <c r="B13" s="26">
+      <c r="B13" s="362">
         <v>0.073909473540669554</v>
       </c>
       <c r="C13">
@@ -6652,10 +11692,10 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="27" t="s">
+      <c r="A14" s="363" t="s">
         <v>45</v>
       </c>
-      <c r="B14" s="28">
+      <c r="B14" s="364">
         <v>-0.17812799756767383</v>
       </c>
       <c r="C14">
@@ -6753,10 +11793,10 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="29" t="s">
+      <c r="A15" s="365" t="s">
         <v>46</v>
       </c>
-      <c r="B15" s="30">
+      <c r="B15" s="366">
         <v>0.075289601696469061</v>
       </c>
       <c r="C15">
@@ -6854,10 +11894,10 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="31" t="s">
+      <c r="A16" s="367" t="s">
         <v>47</v>
       </c>
-      <c r="B16" s="32">
+      <c r="B16" s="368">
         <v>0.66483359576215129</v>
       </c>
       <c r="C16">
@@ -6955,10 +11995,10 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="33" t="s">
+      <c r="A17" s="369" t="s">
         <v>48</v>
       </c>
-      <c r="B17" s="34">
+      <c r="B17" s="370">
         <v>0.20214936947847398</v>
       </c>
       <c r="C17">
@@ -7056,10 +12096,10 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="35" t="s">
+      <c r="A18" s="371" t="s">
         <v>49</v>
       </c>
-      <c r="B18" s="36">
+      <c r="B18" s="372">
         <v>0.37982441199027994</v>
       </c>
       <c r="C18">
@@ -7157,10 +12197,10 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="37" t="s">
+      <c r="A19" s="373" t="s">
         <v>50</v>
       </c>
-      <c r="B19" s="38">
+      <c r="B19" s="374">
         <v>0.54124242179950766</v>
       </c>
       <c r="C19">
@@ -7258,10 +12298,10 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="39" t="s">
+      <c r="A20" s="375" t="s">
         <v>51</v>
       </c>
-      <c r="B20" s="40">
+      <c r="B20" s="376">
         <v>0.57473972881196844</v>
       </c>
       <c r="C20">
@@ -7359,10 +12399,10 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="41" t="s">
+      <c r="A21" s="377" t="s">
         <v>52</v>
       </c>
-      <c r="B21" s="42">
+      <c r="B21" s="378">
         <v>-1.6564019302568576</v>
       </c>
       <c r="C21">
@@ -7460,10 +12500,10 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="43" t="s">
+      <c r="A22" s="379" t="s">
         <v>53</v>
       </c>
-      <c r="B22" s="44">
+      <c r="B22" s="380">
         <v>0.54792293821008509</v>
       </c>
       <c r="C22">
@@ -7561,10 +12601,10 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="45" t="s">
+      <c r="A23" s="381" t="s">
         <v>54</v>
       </c>
-      <c r="B23" s="46">
+      <c r="B23" s="382">
         <v>0.035398033068527117</v>
       </c>
       <c r="C23">
@@ -7662,10 +12702,10 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="47" t="s">
+      <c r="A24" s="383" t="s">
         <v>55</v>
       </c>
-      <c r="B24" s="48">
+      <c r="B24" s="384">
         <v>0.00047417505000568115</v>
       </c>
       <c r="C24">
@@ -7763,10 +12803,10 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="49" t="s">
+      <c r="A25" s="385" t="s">
         <v>56</v>
       </c>
-      <c r="B25" s="50">
+      <c r="B25" s="386">
         <v>0.27946643957541661</v>
       </c>
       <c r="C25">
@@ -7864,10 +12904,10 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="51" t="s">
+      <c r="A26" s="387" t="s">
         <v>57</v>
       </c>
-      <c r="B26" s="52">
+      <c r="B26" s="388">
         <v>0.22332089465244645</v>
       </c>
       <c r="C26">
@@ -7965,10 +13005,10 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="53" t="s">
+      <c r="A27" s="389" t="s">
         <v>58</v>
       </c>
-      <c r="B27" s="54">
+      <c r="B27" s="390">
         <v>0.3725176900703322</v>
       </c>
       <c r="C27">
@@ -8066,10 +13106,10 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="55" t="s">
+      <c r="A28" s="391" t="s">
         <v>59</v>
       </c>
-      <c r="B28" s="56">
+      <c r="B28" s="392">
         <v>0.91632463334078373</v>
       </c>
       <c r="C28">
@@ -8167,10 +13207,10 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="57" t="s">
+      <c r="A29" s="393" t="s">
         <v>60</v>
       </c>
-      <c r="B29" s="58">
+      <c r="B29" s="394">
         <v>-0.48648583195173456</v>
       </c>
       <c r="C29">
@@ -8268,10 +13308,10 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="59" t="s">
+      <c r="A30" s="395" t="s">
         <v>61</v>
       </c>
-      <c r="B30" s="60">
+      <c r="B30" s="396">
         <v>0.67874799810790676</v>
       </c>
       <c r="C30">
@@ -8369,10 +13409,10 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="61" t="s">
+      <c r="A31" s="397" t="s">
         <v>62</v>
       </c>
-      <c r="B31" s="62">
+      <c r="B31" s="398">
         <v>-0.14810867233854183</v>
       </c>
       <c r="C31">
@@ -8470,10 +13510,10 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="63" t="s">
+      <c r="A32" s="399" t="s">
         <v>63</v>
       </c>
-      <c r="B32" s="64">
+      <c r="B32" s="400">
         <v>14.687739664725413</v>
       </c>
       <c r="C32">
@@ -8580,10 +13620,10 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="65" t="s">
+      <c r="A1" s="401" t="s">
         <v>32</v>
       </c>
-      <c r="B1" s="66" t="s">
+      <c r="B1" s="402" t="s">
         <v>64</v>
       </c>
       <c r="C1" t="s">
@@ -8621,11 +13661,11 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="67" t="s">
+      <c r="A2" s="403" t="s">
         <v>65</v>
       </c>
-      <c r="B2" s="68">
-        <v>-1.916029194190614</v>
+      <c r="B2" s="404">
+        <v>-1.9160291941906147</v>
       </c>
       <c r="C2">
         <v>0.053315883507596265</v>
@@ -8662,17 +13702,17 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="69" t="s">
+      <c r="A3" s="405" t="s">
         <v>66</v>
       </c>
-      <c r="B3" s="70">
-        <v>0.51190217053103704</v>
+      <c r="B3" s="406">
+        <v>0.51190217053103715</v>
       </c>
       <c r="C3">
         <v>0</v>
       </c>
       <c r="D3">
-        <v>0.047494112831108638</v>
+        <v>0.047494112831108617</v>
       </c>
       <c r="E3">
         <v>0</v>
@@ -8703,10 +13743,10 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="71" t="s">
+      <c r="A4" s="407" t="s">
         <v>67</v>
       </c>
-      <c r="B4" s="72">
+      <c r="B4" s="408">
         <v>-1.313019961490423</v>
       </c>
       <c r="C4">
@@ -8716,7 +13756,7 @@
         <v>0</v>
       </c>
       <c r="E4">
-        <v>0.054495470104473989</v>
+        <v>0.054495470104474003</v>
       </c>
       <c r="F4">
         <v>0</v>
@@ -8744,11 +13784,11 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="73" t="s">
+      <c r="A5" s="409" t="s">
         <v>68</v>
       </c>
-      <c r="B5" s="74">
-        <v>0.092381706981734174</v>
+      <c r="B5" s="410">
+        <v>0.092381706981734188</v>
       </c>
       <c r="C5">
         <v>0</v>
@@ -8760,7 +13800,7 @@
         <v>0</v>
       </c>
       <c r="F5">
-        <v>0.031334215549360271</v>
+        <v>0.031334215549360278</v>
       </c>
       <c r="G5">
         <v>0</v>
@@ -8785,11 +13825,11 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="75" t="s">
+      <c r="A6" s="411" t="s">
         <v>69</v>
       </c>
-      <c r="B6" s="76">
-        <v>0.025587379897433003</v>
+      <c r="B6" s="412">
+        <v>0.025587379897433444</v>
       </c>
       <c r="C6">
         <v>0</v>
@@ -8804,7 +13844,7 @@
         <v>0</v>
       </c>
       <c r="G6">
-        <v>0.031655738868466954</v>
+        <v>0.031655738868466968</v>
       </c>
       <c r="H6">
         <v>0</v>
@@ -8826,11 +13866,11 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="77" t="s">
+      <c r="A7" s="413" t="s">
         <v>70</v>
       </c>
-      <c r="B7" s="78">
-        <v>0.22142730941148792</v>
+      <c r="B7" s="414">
+        <v>0.22142730941148836</v>
       </c>
       <c r="C7">
         <v>0</v>
@@ -8848,7 +13888,7 @@
         <v>0</v>
       </c>
       <c r="H7">
-        <v>0.044261929272442081</v>
+        <v>0.044261929272442088</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -8867,11 +13907,11 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="79" t="s">
+      <c r="A8" s="415" t="s">
         <v>71</v>
       </c>
-      <c r="B8" s="80">
-        <v>-0.068995892644541396</v>
+      <c r="B8" s="416">
+        <v>-0.068995892644541479</v>
       </c>
       <c r="C8">
         <v>0</v>
@@ -8892,7 +13932,7 @@
         <v>0</v>
       </c>
       <c r="I8">
-        <v>0.0056411497125225425</v>
+        <v>0.0056411497125225443</v>
       </c>
       <c r="J8">
         <v>0</v>
@@ -8908,11 +13948,11 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="81" t="s">
+      <c r="A9" s="417" t="s">
         <v>72</v>
       </c>
-      <c r="B9" s="82">
-        <v>-0.043090703250210194</v>
+      <c r="B9" s="418">
+        <v>-0.043090703250210562</v>
       </c>
       <c r="C9">
         <v>0</v>
@@ -8936,7 +13976,7 @@
         <v>0</v>
       </c>
       <c r="J9">
-        <v>0.0077162225476205886</v>
+        <v>0.0077162225476205938</v>
       </c>
       <c r="K9">
         <v>0</v>
@@ -8949,10 +13989,10 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="83" t="s">
+      <c r="A10" s="419" t="s">
         <v>73</v>
       </c>
-      <c r="B10" s="84">
+      <c r="B10" s="420">
         <v>-3.3040169957372143</v>
       </c>
       <c r="C10">
@@ -8980,7 +14020,7 @@
         <v>0</v>
       </c>
       <c r="K10">
-        <v>0.027652677186717309</v>
+        <v>0.027652677186717316</v>
       </c>
       <c r="L10">
         <v>0</v>
@@ -8990,11 +14030,11 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="85" t="s">
+      <c r="A11" s="421" t="s">
         <v>74</v>
       </c>
-      <c r="B11" s="86">
-        <v>-0.66759841791019148</v>
+      <c r="B11" s="422">
+        <v>-0.66759841791019037</v>
       </c>
       <c r="C11">
         <v>0</v>
@@ -9031,11 +14071,11 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="87" t="s">
+      <c r="A12" s="423" t="s">
         <v>75</v>
       </c>
-      <c r="B12" s="88">
-        <v>-0.33664732228534444</v>
+      <c r="B12" s="424">
+        <v>-0.33664732228534316</v>
       </c>
       <c r="C12">
         <v>0</v>
@@ -9068,7 +14108,7 @@
         <v>0</v>
       </c>
       <c r="M12">
-        <v>0.020000894891558541</v>
+        <v>0.020000894891558544</v>
       </c>
     </row>
   </sheetData>
@@ -9081,10 +14121,10 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="89" t="s">
+      <c r="A1" s="425" t="s">
         <v>32</v>
       </c>
-      <c r="B1" s="90" t="s">
+      <c r="B1" s="426" t="s">
         <v>64</v>
       </c>
       <c r="C1" t="s">
@@ -9122,10 +14162,10 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="91" t="s">
+      <c r="A2" s="427" t="s">
         <v>65</v>
       </c>
-      <c r="B2" s="92">
+      <c r="B2" s="428">
         <v>-2.6085095668087694</v>
       </c>
       <c r="C2">
@@ -9163,17 +14203,17 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="93" t="s">
+      <c r="A3" s="429" t="s">
         <v>66</v>
       </c>
-      <c r="B3" s="94">
-        <v>0.07398438684850997</v>
+      <c r="B3" s="430">
+        <v>0.073984386848508624</v>
       </c>
       <c r="C3">
         <v>0</v>
       </c>
       <c r="D3">
-        <v>0.090461960902035385</v>
+        <v>0.090461960902035343</v>
       </c>
       <c r="E3">
         <v>0</v>
@@ -9204,11 +14244,11 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="95" t="s">
+      <c r="A4" s="431" t="s">
         <v>67</v>
       </c>
-      <c r="B4" s="96">
-        <v>-2.9375172462468759</v>
+      <c r="B4" s="432">
+        <v>-2.9375172462468777</v>
       </c>
       <c r="C4">
         <v>0</v>
@@ -9217,7 +14257,7 @@
         <v>0</v>
       </c>
       <c r="E4">
-        <v>0.16792151771142541</v>
+        <v>0.16792151771142536</v>
       </c>
       <c r="F4">
         <v>0</v>
@@ -9245,10 +14285,10 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="97" t="s">
+      <c r="A5" s="433" t="s">
         <v>68</v>
       </c>
-      <c r="B5" s="98">
+      <c r="B5" s="434">
         <v>-0.12726580900610276</v>
       </c>
       <c r="C5">
@@ -9261,7 +14301,7 @@
         <v>0</v>
       </c>
       <c r="F5">
-        <v>0.038218653135434419</v>
+        <v>0.03821865313543444</v>
       </c>
       <c r="G5">
         <v>0</v>
@@ -9286,11 +14326,11 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="99" t="s">
+      <c r="A6" s="435" t="s">
         <v>69</v>
       </c>
-      <c r="B6" s="100">
-        <v>-0.030983772131493555</v>
+      <c r="B6" s="436">
+        <v>-0.030983772131493833</v>
       </c>
       <c r="C6">
         <v>0</v>
@@ -9305,7 +14345,7 @@
         <v>0</v>
       </c>
       <c r="G6">
-        <v>0.035478868602598322</v>
+        <v>0.035478868602598315</v>
       </c>
       <c r="H6">
         <v>0</v>
@@ -9327,11 +14367,11 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="101" t="s">
+      <c r="A7" s="437" t="s">
         <v>70</v>
       </c>
-      <c r="B7" s="102">
-        <v>0.46323257013636254</v>
+      <c r="B7" s="438">
+        <v>0.4632325701363621</v>
       </c>
       <c r="C7">
         <v>0</v>
@@ -9368,11 +14408,11 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="103" t="s">
+      <c r="A8" s="439" t="s">
         <v>71</v>
       </c>
-      <c r="B8" s="104">
-        <v>-0.19273596672164445</v>
+      <c r="B8" s="440">
+        <v>-0.19273596672164442</v>
       </c>
       <c r="C8">
         <v>0</v>
@@ -9393,7 +14433,7 @@
         <v>0</v>
       </c>
       <c r="I8">
-        <v>0.0053689964580343067</v>
+        <v>0.0053689964580343049</v>
       </c>
       <c r="J8">
         <v>0</v>
@@ -9409,11 +14449,11 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="105" t="s">
+      <c r="A9" s="441" t="s">
         <v>72</v>
       </c>
-      <c r="B9" s="106">
-        <v>-0.1341738169470226</v>
+      <c r="B9" s="442">
+        <v>-0.13417381694702252</v>
       </c>
       <c r="C9">
         <v>0</v>
@@ -9437,7 +14477,7 @@
         <v>0</v>
       </c>
       <c r="J9">
-        <v>0.0059382109132955141</v>
+        <v>0.0059382109132955123</v>
       </c>
       <c r="K9">
         <v>0</v>
@@ -9450,10 +14490,10 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="107" t="s">
+      <c r="A10" s="443" t="s">
         <v>73</v>
       </c>
-      <c r="B10" s="108">
+      <c r="B10" s="444">
         <v>-3.1557604416046865</v>
       </c>
       <c r="C10">
@@ -9491,10 +14531,10 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="109" t="s">
+      <c r="A11" s="445" t="s">
         <v>74</v>
       </c>
-      <c r="B11" s="110">
+      <c r="B11" s="446">
         <v>-0.23563099770913443</v>
       </c>
       <c r="C11">
@@ -9532,11 +14572,11 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="111" t="s">
+      <c r="A12" s="447" t="s">
         <v>75</v>
       </c>
-      <c r="B12" s="112">
-        <v>-0.064898119010264613</v>
+      <c r="B12" s="448">
+        <v>-0.064898119010264738</v>
       </c>
       <c r="C12">
         <v>0</v>
@@ -9582,10 +14622,10 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="113" t="s">
+      <c r="A1" s="449" t="s">
         <v>32</v>
       </c>
-      <c r="B1" s="114" t="s">
+      <c r="B1" s="450" t="s">
         <v>64</v>
       </c>
       <c r="C1" t="s">
@@ -9683,10 +14723,10 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="115" t="s">
+      <c r="A2" s="451" t="s">
         <v>33</v>
       </c>
-      <c r="B2" s="116">
+      <c r="B2" s="452">
         <v>0.71459629585557716</v>
       </c>
       <c r="C2">
@@ -9784,10 +14824,10 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="117" t="s">
+      <c r="A3" s="453" t="s">
         <v>34</v>
       </c>
-      <c r="B3" s="118">
+      <c r="B3" s="454">
         <v>0.051601542217308234</v>
       </c>
       <c r="C3">
@@ -9885,10 +14925,10 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="119" t="s">
+      <c r="A4" s="455" t="s">
         <v>35</v>
       </c>
-      <c r="B4" s="120">
+      <c r="B4" s="456">
         <v>0.077874546680031687</v>
       </c>
       <c r="C4">
@@ -9986,10 +15026,10 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="121" t="s">
+      <c r="A5" s="457" t="s">
         <v>53</v>
       </c>
-      <c r="B5" s="122">
+      <c r="B5" s="458">
         <v>0.11011256840282732</v>
       </c>
       <c r="C5">
@@ -10087,10 +15127,10 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="123" t="s">
+      <c r="A6" s="459" t="s">
         <v>37</v>
       </c>
-      <c r="B6" s="124">
+      <c r="B6" s="460">
         <v>-0.27586090239283467</v>
       </c>
       <c r="C6">
@@ -10188,10 +15228,10 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="125" t="s">
+      <c r="A7" s="461" t="s">
         <v>38</v>
       </c>
-      <c r="B7" s="126">
+      <c r="B7" s="462">
         <v>-0.39525824921737368</v>
       </c>
       <c r="C7">
@@ -10289,10 +15329,10 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="127" t="s">
+      <c r="A8" s="463" t="s">
         <v>39</v>
       </c>
-      <c r="B8" s="128">
+      <c r="B8" s="464">
         <v>-0.14676753260654513</v>
       </c>
       <c r="C8">
@@ -10390,10 +15430,10 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="129" t="s">
+      <c r="A9" s="465" t="s">
         <v>40</v>
       </c>
-      <c r="B9" s="130">
+      <c r="B9" s="466">
         <v>-0.21913292747489163</v>
       </c>
       <c r="C9">
@@ -10491,10 +15531,10 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="131" t="s">
+      <c r="A10" s="467" t="s">
         <v>41</v>
       </c>
-      <c r="B10" s="132">
+      <c r="B10" s="468">
         <v>-0.17354204104168353</v>
       </c>
       <c r="C10">
@@ -10592,10 +15632,10 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="133" t="s">
+      <c r="A11" s="469" t="s">
         <v>42</v>
       </c>
-      <c r="B11" s="134">
+      <c r="B11" s="470">
         <v>-0.11143261294530343</v>
       </c>
       <c r="C11">
@@ -10693,10 +15733,10 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="135" t="s">
+      <c r="A12" s="471" t="s">
         <v>43</v>
       </c>
-      <c r="B12" s="136">
+      <c r="B12" s="472">
         <v>-0.060986810592122929</v>
       </c>
       <c r="C12">
@@ -10794,10 +15834,10 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="137" t="s">
+      <c r="A13" s="473" t="s">
         <v>44</v>
       </c>
-      <c r="B13" s="138">
+      <c r="B13" s="474">
         <v>-0.052801683583641089</v>
       </c>
       <c r="C13">
@@ -10895,10 +15935,10 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="139" t="s">
+      <c r="A14" s="475" t="s">
         <v>45</v>
       </c>
-      <c r="B14" s="140">
+      <c r="B14" s="476">
         <v>-0.21541736198078901</v>
       </c>
       <c r="C14">
@@ -10996,10 +16036,10 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="141" t="s">
+      <c r="A15" s="477" t="s">
         <v>46</v>
       </c>
-      <c r="B15" s="142">
+      <c r="B15" s="478">
         <v>-0.081148358846952304</v>
       </c>
       <c r="C15">
@@ -11097,10 +16137,10 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="143" t="s">
+      <c r="A16" s="479" t="s">
         <v>47</v>
       </c>
-      <c r="B16" s="144">
+      <c r="B16" s="480">
         <v>-0.37522535503919469</v>
       </c>
       <c r="C16">
@@ -11198,10 +16238,10 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="145" t="s">
+      <c r="A17" s="481" t="s">
         <v>48</v>
       </c>
-      <c r="B17" s="146">
+      <c r="B17" s="482">
         <v>0.15630708692198164</v>
       </c>
       <c r="C17">
@@ -11299,10 +16339,10 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="147" t="s">
+      <c r="A18" s="483" t="s">
         <v>49</v>
       </c>
-      <c r="B18" s="148">
+      <c r="B18" s="484">
         <v>0.52983485456413804</v>
       </c>
       <c r="C18">
@@ -11400,10 +16440,10 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="149" t="s">
+      <c r="A19" s="485" t="s">
         <v>50</v>
       </c>
-      <c r="B19" s="150">
+      <c r="B19" s="486">
         <v>0.67535673896084703</v>
       </c>
       <c r="C19">
@@ -11501,10 +16541,10 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="151" t="s">
+      <c r="A20" s="487" t="s">
         <v>51</v>
       </c>
-      <c r="B20" s="152">
+      <c r="B20" s="488">
         <v>0.87812586999915254</v>
       </c>
       <c r="C20">
@@ -11602,10 +16642,10 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="153" t="s">
+      <c r="A21" s="489" t="s">
         <v>52</v>
       </c>
-      <c r="B21" s="154">
+      <c r="B21" s="490">
         <v>-2.7113359910745429</v>
       </c>
       <c r="C21">
@@ -11703,10 +16743,10 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="155" t="s">
+      <c r="A22" s="491" t="s">
         <v>36</v>
       </c>
-      <c r="B22" s="156">
+      <c r="B22" s="492">
         <v>0.65979952120054097</v>
       </c>
       <c r="C22">
@@ -11804,10 +16844,10 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="157" t="s">
+      <c r="A23" s="493" t="s">
         <v>54</v>
       </c>
-      <c r="B23" s="158">
+      <c r="B23" s="494">
         <v>-0.018787926985859835</v>
       </c>
       <c r="C23">
@@ -11905,10 +16945,10 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="159" t="s">
+      <c r="A24" s="495" t="s">
         <v>55</v>
       </c>
-      <c r="B24" s="160">
+      <c r="B24" s="496">
         <v>-0.00080898544056616257</v>
       </c>
       <c r="C24">
@@ -12006,10 +17046,10 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="161" t="s">
+      <c r="A25" s="497" t="s">
         <v>56</v>
       </c>
-      <c r="B25" s="162">
+      <c r="B25" s="498">
         <v>-0.52931057254925273</v>
       </c>
       <c r="C25">
@@ -12107,10 +17147,10 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="163" t="s">
+      <c r="A26" s="499" t="s">
         <v>57</v>
       </c>
-      <c r="B26" s="164">
+      <c r="B26" s="500">
         <v>-0.76690615788534566</v>
       </c>
       <c r="C26">
@@ -12208,10 +17248,10 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="165" t="s">
+      <c r="A27" s="501" t="s">
         <v>58</v>
       </c>
-      <c r="B27" s="166">
+      <c r="B27" s="502">
         <v>-0.71917528977230905</v>
       </c>
       <c r="C27">
@@ -12309,10 +17349,10 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="167" t="s">
+      <c r="A28" s="503" t="s">
         <v>59</v>
       </c>
-      <c r="B28" s="168">
+      <c r="B28" s="504">
         <v>-0.054874677473126202</v>
       </c>
       <c r="C28">
@@ -12410,10 +17450,10 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="169" t="s">
+      <c r="A29" s="505" t="s">
         <v>60</v>
       </c>
-      <c r="B29" s="170">
+      <c r="B29" s="506">
         <v>-0.060587760376332282</v>
       </c>
       <c r="C29">
@@ -12511,10 +17551,10 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="171" t="s">
+      <c r="A30" s="507" t="s">
         <v>61</v>
       </c>
-      <c r="B30" s="172">
+      <c r="B30" s="508">
         <v>0.12204059858267877</v>
       </c>
       <c r="C30">
@@ -12612,10 +17652,10 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="173" t="s">
+      <c r="A31" s="509" t="s">
         <v>62</v>
       </c>
-      <c r="B31" s="174">
+      <c r="B31" s="510">
         <v>-0.0061844678815005183</v>
       </c>
       <c r="C31">
@@ -12713,10 +17753,10 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="175" t="s">
+      <c r="A32" s="511" t="s">
         <v>63</v>
       </c>
-      <c r="B32" s="176">
+      <c r="B32" s="512">
         <v>14.168939220001604</v>
       </c>
       <c r="C32">
@@ -12823,10 +17863,10 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="177" t="s">
+      <c r="A1" s="513" t="s">
         <v>32</v>
       </c>
-      <c r="B1" s="178" t="s">
+      <c r="B1" s="514" t="s">
         <v>64</v>
       </c>
       <c r="C1" t="s">
@@ -12864,14 +17904,14 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="179" t="s">
+      <c r="A2" s="515" t="s">
         <v>65</v>
       </c>
-      <c r="B2" s="180">
-        <v>-1.20487073743697</v>
+      <c r="B2" s="516">
+        <v>-1.2048707374369696</v>
       </c>
       <c r="C2">
-        <v>0.04575700243377178</v>
+        <v>0.045757002433771767</v>
       </c>
       <c r="D2">
         <v>0</v>
@@ -12905,11 +17945,11 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="181" t="s">
+      <c r="A3" s="517" t="s">
         <v>66</v>
       </c>
-      <c r="B3" s="182">
-        <v>0.16374224724440792</v>
+      <c r="B3" s="518">
+        <v>0.16374224724440825</v>
       </c>
       <c r="C3">
         <v>0</v>
@@ -12946,11 +17986,11 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="183" t="s">
+      <c r="A4" s="519" t="s">
         <v>67</v>
       </c>
-      <c r="B4" s="184">
-        <v>-1.27017867083001</v>
+      <c r="B4" s="520">
+        <v>-1.2701786708300093</v>
       </c>
       <c r="C4">
         <v>0</v>
@@ -12959,7 +17999,7 @@
         <v>0</v>
       </c>
       <c r="E4">
-        <v>0.050157244720716705</v>
+        <v>0.050157244720716677</v>
       </c>
       <c r="F4">
         <v>0</v>
@@ -12987,11 +18027,11 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="185" t="s">
+      <c r="A5" s="521" t="s">
         <v>68</v>
       </c>
-      <c r="B5" s="186">
-        <v>-0.067164416597812693</v>
+      <c r="B5" s="522">
+        <v>-0.06716441659781279</v>
       </c>
       <c r="C5">
         <v>0</v>
@@ -13028,11 +18068,11 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="187" t="s">
+      <c r="A6" s="523" t="s">
         <v>69</v>
       </c>
-      <c r="B6" s="188">
-        <v>-0.1127400764600988</v>
+      <c r="B6" s="524">
+        <v>-0.11274007646009894</v>
       </c>
       <c r="C6">
         <v>0</v>
@@ -13047,7 +18087,7 @@
         <v>0</v>
       </c>
       <c r="G6">
-        <v>0.025227931203029158</v>
+        <v>0.025227931203029141</v>
       </c>
       <c r="H6">
         <v>0</v>
@@ -13069,11 +18109,11 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="189" t="s">
+      <c r="A7" s="525" t="s">
         <v>70</v>
       </c>
-      <c r="B7" s="190">
-        <v>-0.013654678891171871</v>
+      <c r="B7" s="526">
+        <v>-0.013654678891172225</v>
       </c>
       <c r="C7">
         <v>0</v>
@@ -13091,7 +18131,7 @@
         <v>0</v>
       </c>
       <c r="H7">
-        <v>0.040624533741025703</v>
+        <v>0.040624533741025669</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -13110,11 +18150,11 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="191" t="s">
+      <c r="A8" s="527" t="s">
         <v>71</v>
       </c>
-      <c r="B8" s="192">
-        <v>0.060596429348527325</v>
+      <c r="B8" s="528">
+        <v>0.060596429348527395</v>
       </c>
       <c r="C8">
         <v>0</v>
@@ -13135,7 +18175,7 @@
         <v>0</v>
       </c>
       <c r="I8">
-        <v>0.0036808347583151386</v>
+        <v>0.0036808347583151368</v>
       </c>
       <c r="J8">
         <v>0</v>
@@ -13151,11 +18191,11 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="193" t="s">
+      <c r="A9" s="529" t="s">
         <v>72</v>
       </c>
-      <c r="B9" s="194">
-        <v>0.082188386710631445</v>
+      <c r="B9" s="530">
+        <v>0.082188386710631542</v>
       </c>
       <c r="C9">
         <v>0</v>
@@ -13179,7 +18219,7 @@
         <v>0</v>
       </c>
       <c r="J9">
-        <v>0.0047385339366014115</v>
+        <v>0.0047385339366014098</v>
       </c>
       <c r="K9">
         <v>0</v>
@@ -13192,11 +18232,11 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="195" t="s">
+      <c r="A10" s="531" t="s">
         <v>73</v>
       </c>
-      <c r="B10" s="196">
-        <v>-0.093380622011006123</v>
+      <c r="B10" s="532">
+        <v>-0.093380622011006248</v>
       </c>
       <c r="C10">
         <v>0</v>
@@ -13223,7 +18263,7 @@
         <v>0</v>
       </c>
       <c r="K10">
-        <v>0.020344193908769164</v>
+        <v>0.020344193908769168</v>
       </c>
       <c r="L10">
         <v>0</v>
@@ -13233,10 +18273,10 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="197" t="s">
+      <c r="A11" s="533" t="s">
         <v>74</v>
       </c>
-      <c r="B11" s="198">
+      <c r="B11" s="534">
         <v>0.71802828058220325</v>
       </c>
       <c r="C11">
@@ -13274,11 +18314,11 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="199" t="s">
+      <c r="A12" s="535" t="s">
         <v>75</v>
       </c>
-      <c r="B12" s="200">
-        <v>0.60704486660469581</v>
+      <c r="B12" s="536">
+        <v>0.60704486660469548</v>
       </c>
       <c r="C12">
         <v>0</v>
@@ -13311,7 +18351,7 @@
         <v>0</v>
       </c>
       <c r="M12">
-        <v>0.011375591799474888</v>
+        <v>0.01137559179947489</v>
       </c>
     </row>
   </sheetData>
@@ -13324,10 +18364,10 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="201" t="s">
+      <c r="A1" s="537" t="s">
         <v>32</v>
       </c>
-      <c r="B1" s="202" t="s">
+      <c r="B1" s="538" t="s">
         <v>64</v>
       </c>
       <c r="C1" t="s">
@@ -13365,14 +18405,14 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="203" t="s">
+      <c r="A2" s="539" t="s">
         <v>65</v>
       </c>
-      <c r="B2" s="204">
+      <c r="B2" s="540">
         <v>-0.9753686953883135</v>
       </c>
       <c r="C2">
-        <v>0.074514045144474447</v>
+        <v>0.074514045144474433</v>
       </c>
       <c r="D2">
         <v>0</v>
@@ -13406,17 +18446,17 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="205" t="s">
+      <c r="A3" s="541" t="s">
         <v>66</v>
       </c>
-      <c r="B3" s="206">
-        <v>-0.15292874468161566</v>
+      <c r="B3" s="542">
+        <v>-0.15292874468161533</v>
       </c>
       <c r="C3">
         <v>0</v>
       </c>
       <c r="D3">
-        <v>0.06201974842465504</v>
+        <v>0.062019748424655075</v>
       </c>
       <c r="E3">
         <v>0</v>
@@ -13447,11 +18487,11 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="207" t="s">
+      <c r="A4" s="543" t="s">
         <v>67</v>
       </c>
-      <c r="B4" s="208">
-        <v>-2.0082806708784569</v>
+      <c r="B4" s="544">
+        <v>-2.0082806708784564</v>
       </c>
       <c r="C4">
         <v>0</v>
@@ -13460,7 +18500,7 @@
         <v>0</v>
       </c>
       <c r="E4">
-        <v>0.14898119105005941</v>
+        <v>0.1489811910500595</v>
       </c>
       <c r="F4">
         <v>0</v>
@@ -13488,11 +18528,11 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="209" t="s">
+      <c r="A5" s="545" t="s">
         <v>68</v>
       </c>
-      <c r="B5" s="210">
-        <v>0.14436623151580438</v>
+      <c r="B5" s="546">
+        <v>0.1443662315158043</v>
       </c>
       <c r="C5">
         <v>0</v>
@@ -13504,7 +18544,7 @@
         <v>0</v>
       </c>
       <c r="F5">
-        <v>0.026468818964130655</v>
+        <v>0.026468818964130648</v>
       </c>
       <c r="G5">
         <v>0</v>
@@ -13529,11 +18569,11 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="211" t="s">
+      <c r="A6" s="547" t="s">
         <v>69</v>
       </c>
-      <c r="B6" s="212">
-        <v>0.16831778838425832</v>
+      <c r="B6" s="548">
+        <v>0.16831778838425812</v>
       </c>
       <c r="C6">
         <v>0</v>
@@ -13548,7 +18588,7 @@
         <v>0</v>
       </c>
       <c r="G6">
-        <v>0.027506975923140397</v>
+        <v>0.027506975923140387</v>
       </c>
       <c r="H6">
         <v>0</v>
@@ -13570,11 +18610,11 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="213" t="s">
+      <c r="A7" s="549" t="s">
         <v>70</v>
       </c>
-      <c r="B7" s="214">
-        <v>-0.15666303775361107</v>
+      <c r="B7" s="550">
+        <v>-0.15666303775361148</v>
       </c>
       <c r="C7">
         <v>0</v>
@@ -13592,7 +18632,7 @@
         <v>0</v>
       </c>
       <c r="H7">
-        <v>0.048505860510392358</v>
+        <v>0.048505860510392365</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -13611,11 +18651,11 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="215" t="s">
+      <c r="A8" s="551" t="s">
         <v>71</v>
       </c>
-      <c r="B8" s="216">
-        <v>0.041306628088144288</v>
+      <c r="B8" s="552">
+        <v>0.041306628088144233</v>
       </c>
       <c r="C8">
         <v>0</v>
@@ -13652,11 +18692,11 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="217" t="s">
+      <c r="A9" s="553" t="s">
         <v>72</v>
       </c>
-      <c r="B9" s="218">
-        <v>-0.042254584016872182</v>
+      <c r="B9" s="554">
+        <v>-0.042254584016872258</v>
       </c>
       <c r="C9">
         <v>0</v>
@@ -13680,7 +18720,7 @@
         <v>0</v>
       </c>
       <c r="J9">
-        <v>0.0052984575003943313</v>
+        <v>0.0052984575003943339</v>
       </c>
       <c r="K9">
         <v>0</v>
@@ -13693,11 +18733,11 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="219" t="s">
+      <c r="A10" s="555" t="s">
         <v>73</v>
       </c>
-      <c r="B10" s="220">
-        <v>-0.32665570236839503</v>
+      <c r="B10" s="556">
+        <v>-0.32665570236839481</v>
       </c>
       <c r="C10">
         <v>0</v>
@@ -13734,11 +18774,11 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="221" t="s">
+      <c r="A11" s="557" t="s">
         <v>74</v>
       </c>
-      <c r="B11" s="222">
-        <v>0.4019850565280127</v>
+      <c r="B11" s="558">
+        <v>0.40198505652801253</v>
       </c>
       <c r="C11">
         <v>0</v>
@@ -13775,10 +18815,10 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="223" t="s">
+      <c r="A12" s="559" t="s">
         <v>75</v>
       </c>
-      <c r="B12" s="224">
+      <c r="B12" s="560">
         <v>0.22636229223548471</v>
       </c>
       <c r="C12">
@@ -13825,10 +18865,10 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="225" t="s">
+      <c r="A1" s="561" t="s">
         <v>32</v>
       </c>
-      <c r="B1" s="226" t="s">
+      <c r="B1" s="562" t="s">
         <v>64</v>
       </c>
       <c r="C1" t="s">
@@ -13926,10 +18966,10 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="227" t="s">
+      <c r="A2" s="563" t="s">
         <v>33</v>
       </c>
-      <c r="B2" s="228">
+      <c r="B2" s="564">
         <v>0.18416314791913194</v>
       </c>
       <c r="C2">
@@ -14027,10 +19067,10 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="229" t="s">
+      <c r="A3" s="565" t="s">
         <v>34</v>
       </c>
-      <c r="B3" s="230">
+      <c r="B3" s="566">
         <v>-0.182049320781206</v>
       </c>
       <c r="C3">
@@ -14128,10 +19168,10 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="231" t="s">
+      <c r="A4" s="567" t="s">
         <v>35</v>
       </c>
-      <c r="B4" s="232">
+      <c r="B4" s="568">
         <v>0.0030882069601683663</v>
       </c>
       <c r="C4">
@@ -14229,10 +19269,10 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="233" t="s">
+      <c r="A5" s="569" t="s">
         <v>36</v>
       </c>
-      <c r="B5" s="234">
+      <c r="B5" s="570">
         <v>0.02276196357881289</v>
       </c>
       <c r="C5">
@@ -14330,10 +19370,10 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="235" t="s">
+      <c r="A6" s="571" t="s">
         <v>37</v>
       </c>
-      <c r="B6" s="236">
+      <c r="B6" s="572">
         <v>0.05614699781645708</v>
       </c>
       <c r="C6">
@@ -14431,10 +19471,10 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="237" t="s">
+      <c r="A7" s="573" t="s">
         <v>38</v>
       </c>
-      <c r="B7" s="238">
+      <c r="B7" s="574">
         <v>0.025431243693189446</v>
       </c>
       <c r="C7">
@@ -14532,10 +19572,10 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="239" t="s">
+      <c r="A8" s="575" t="s">
         <v>39</v>
       </c>
-      <c r="B8" s="240">
+      <c r="B8" s="576">
         <v>0.050869204876938537</v>
       </c>
       <c r="C8">
@@ -14633,10 +19673,10 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="241" t="s">
+      <c r="A9" s="577" t="s">
         <v>40</v>
       </c>
-      <c r="B9" s="242">
+      <c r="B9" s="578">
         <v>0.052198478465210391</v>
       </c>
       <c r="C9">
@@ -14734,10 +19774,10 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="243" t="s">
+      <c r="A10" s="579" t="s">
         <v>41</v>
       </c>
-      <c r="B10" s="244">
+      <c r="B10" s="580">
         <v>-0.004506324046889422</v>
       </c>
       <c r="C10">
@@ -14835,10 +19875,10 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="245" t="s">
+      <c r="A11" s="581" t="s">
         <v>42</v>
       </c>
-      <c r="B11" s="246">
+      <c r="B11" s="582">
         <v>0.060092279467382263</v>
       </c>
       <c r="C11">
@@ -14936,10 +19976,10 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="247" t="s">
+      <c r="A12" s="583" t="s">
         <v>43</v>
       </c>
-      <c r="B12" s="248">
+      <c r="B12" s="584">
         <v>0.0318135805028536</v>
       </c>
       <c r="C12">
@@ -15037,10 +20077,10 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="249" t="s">
+      <c r="A13" s="585" t="s">
         <v>44</v>
       </c>
-      <c r="B13" s="250">
+      <c r="B13" s="586">
         <v>0.036504288508486846</v>
       </c>
       <c r="C13">
@@ -15138,10 +20178,10 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="251" t="s">
+      <c r="A14" s="587" t="s">
         <v>45</v>
       </c>
-      <c r="B14" s="252">
+      <c r="B14" s="588">
         <v>-0.012777176293850482</v>
       </c>
       <c r="C14">
@@ -15239,10 +20279,10 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="253" t="s">
+      <c r="A15" s="589" t="s">
         <v>46</v>
       </c>
-      <c r="B15" s="254">
+      <c r="B15" s="590">
         <v>0.034476495721545833</v>
       </c>
       <c r="C15">
@@ -15340,10 +20380,10 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="255" t="s">
+      <c r="A16" s="591" t="s">
         <v>47</v>
       </c>
-      <c r="B16" s="256">
+      <c r="B16" s="592">
         <v>0.21833874413032286</v>
       </c>
       <c r="C16">
@@ -15441,10 +20481,10 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="257" t="s">
+      <c r="A17" s="593" t="s">
         <v>48</v>
       </c>
-      <c r="B17" s="258">
+      <c r="B17" s="594">
         <v>0.07014756547258319</v>
       </c>
       <c r="C17">
@@ -15542,10 +20582,10 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="259" t="s">
+      <c r="A18" s="595" t="s">
         <v>49</v>
       </c>
-      <c r="B18" s="260">
+      <c r="B18" s="596">
         <v>0.11661475373126196</v>
       </c>
       <c r="C18">
@@ -15643,10 +20683,10 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="261" t="s">
+      <c r="A19" s="597" t="s">
         <v>50</v>
       </c>
-      <c r="B19" s="262">
+      <c r="B19" s="598">
         <v>0.17137368232565625</v>
       </c>
       <c r="C19">
@@ -15744,10 +20784,10 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="263" t="s">
+      <c r="A20" s="599" t="s">
         <v>51</v>
       </c>
-      <c r="B20" s="264">
+      <c r="B20" s="600">
         <v>0.24663930571182938</v>
       </c>
       <c r="C20">
@@ -15845,10 +20885,10 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="265" t="s">
+      <c r="A21" s="601" t="s">
         <v>52</v>
       </c>
-      <c r="B21" s="266">
+      <c r="B21" s="602">
         <v>-0.51971148676547196</v>
       </c>
       <c r="C21">
@@ -15946,10 +20986,10 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="267" t="s">
+      <c r="A22" s="603" t="s">
         <v>76</v>
       </c>
-      <c r="B22" s="268">
+      <c r="B22" s="604">
         <v>0.40249440243170043</v>
       </c>
       <c r="C22">
@@ -16047,10 +21087,10 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="269" t="s">
+      <c r="A23" s="605" t="s">
         <v>54</v>
       </c>
-      <c r="B23" s="270">
+      <c r="B23" s="606">
         <v>-0.028279500133225683</v>
       </c>
       <c r="C23">
@@ -16148,10 +21188,10 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="271" t="s">
+      <c r="A24" s="607" t="s">
         <v>55</v>
       </c>
-      <c r="B24" s="272">
+      <c r="B24" s="608">
         <v>0.00039302303831283093</v>
       </c>
       <c r="C24">
@@ -16249,10 +21289,10 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="273" t="s">
+      <c r="A25" s="609" t="s">
         <v>56</v>
       </c>
-      <c r="B25" s="274">
+      <c r="B25" s="610">
         <v>-0.036836820430847225</v>
       </c>
       <c r="C25">
@@ -16350,10 +21390,10 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="275" t="s">
+      <c r="A26" s="611" t="s">
         <v>57</v>
       </c>
-      <c r="B26" s="276">
+      <c r="B26" s="612">
         <v>-0.015683575208522087</v>
       </c>
       <c r="C26">
@@ -16451,10 +21491,10 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="277" t="s">
+      <c r="A27" s="613" t="s">
         <v>58</v>
       </c>
-      <c r="B27" s="278">
+      <c r="B27" s="614">
         <v>-0.015739907522300128</v>
       </c>
       <c r="C27">
@@ -16552,10 +21592,10 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="279" t="s">
+      <c r="A28" s="615" t="s">
         <v>59</v>
       </c>
-      <c r="B28" s="280">
+      <c r="B28" s="616">
         <v>0.037379391139588956</v>
       </c>
       <c r="C28">
@@ -16653,10 +21693,10 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="281" t="s">
+      <c r="A29" s="617" t="s">
         <v>60</v>
       </c>
-      <c r="B29" s="282">
+      <c r="B29" s="618">
         <v>-0.12919790446552198</v>
       </c>
       <c r="C29">
@@ -16754,10 +21794,10 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="283" t="s">
+      <c r="A30" s="619" t="s">
         <v>61</v>
       </c>
-      <c r="B30" s="284">
+      <c r="B30" s="620">
         <v>-0.051654398778955911</v>
       </c>
       <c r="C30">
@@ -16855,10 +21895,10 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="285" t="s">
+      <c r="A31" s="621" t="s">
         <v>62</v>
       </c>
-      <c r="B31" s="286">
+      <c r="B31" s="622">
         <v>-0.013168828277025974</v>
       </c>
       <c r="C31">
@@ -16956,10 +21996,10 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="287" t="s">
+      <c r="A32" s="623" t="s">
         <v>63</v>
       </c>
-      <c r="B32" s="288">
+      <c r="B32" s="624">
         <v>3.3510992342912966</v>
       </c>
       <c r="C32">
@@ -17066,10 +22106,10 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="289" t="s">
+      <c r="A1" s="625" t="s">
         <v>32</v>
       </c>
-      <c r="B1" s="290" t="s">
+      <c r="B1" s="626" t="s">
         <v>64</v>
       </c>
       <c r="C1" t="s">
@@ -17107,10 +22147,10 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="291" t="s">
+      <c r="A2" s="627" t="s">
         <v>65</v>
       </c>
-      <c r="B2" s="292">
+      <c r="B2" s="628">
         <v>-0.33375451909654413</v>
       </c>
       <c r="C2">
@@ -17148,17 +22188,17 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="293" t="s">
+      <c r="A3" s="629" t="s">
         <v>66</v>
       </c>
-      <c r="B3" s="294">
-        <v>0.047234565657565196</v>
+      <c r="B3" s="630">
+        <v>0.047234565657565133</v>
       </c>
       <c r="C3">
         <v>0</v>
       </c>
       <c r="D3">
-        <v>0.002515642006598652</v>
+        <v>0.0025156420065986511</v>
       </c>
       <c r="E3">
         <v>0</v>
@@ -17189,11 +22229,11 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="295" t="s">
+      <c r="A4" s="631" t="s">
         <v>67</v>
       </c>
-      <c r="B4" s="296">
-        <v>-0.22438018247514535</v>
+      <c r="B4" s="632">
+        <v>-0.22438018247514541</v>
       </c>
       <c r="C4">
         <v>0</v>
@@ -17202,7 +22242,7 @@
         <v>0</v>
       </c>
       <c r="E4">
-        <v>0.0027882703866128908</v>
+        <v>0.0027882703866128904</v>
       </c>
       <c r="F4">
         <v>0</v>
@@ -17230,10 +22270,10 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="297" t="s">
+      <c r="A5" s="633" t="s">
         <v>68</v>
       </c>
-      <c r="B5" s="298">
+      <c r="B5" s="634">
         <v>-0.039206561757302159</v>
       </c>
       <c r="C5">
@@ -17246,7 +22286,7 @@
         <v>0</v>
       </c>
       <c r="F5">
-        <v>0.0015301191504978587</v>
+        <v>0.001530119150497858</v>
       </c>
       <c r="G5">
         <v>0</v>
@@ -17271,11 +22311,11 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="299" t="s">
+      <c r="A6" s="635" t="s">
         <v>69</v>
       </c>
-      <c r="B6" s="300">
-        <v>-0.06665226584883191</v>
+      <c r="B6" s="636">
+        <v>-0.06665226584883184</v>
       </c>
       <c r="C6">
         <v>0</v>
@@ -17290,7 +22330,7 @@
         <v>0</v>
       </c>
       <c r="G6">
-        <v>0.0016148871240325971</v>
+        <v>0.0016148871240325977</v>
       </c>
       <c r="H6">
         <v>0</v>
@@ -17312,11 +22352,11 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="301" t="s">
+      <c r="A7" s="637" t="s">
         <v>70</v>
       </c>
-      <c r="B7" s="302">
-        <v>-0.043683646423704252</v>
+      <c r="B7" s="638">
+        <v>-0.043683646423704224</v>
       </c>
       <c r="C7">
         <v>0</v>
@@ -17353,11 +22393,11 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="303" t="s">
+      <c r="A8" s="639" t="s">
         <v>71</v>
       </c>
-      <c r="B8" s="304">
-        <v>-0.026860125116087177</v>
+      <c r="B8" s="640">
+        <v>-0.026860125116087166</v>
       </c>
       <c r="C8">
         <v>0</v>
@@ -17378,7 +22418,7 @@
         <v>0</v>
       </c>
       <c r="I8">
-        <v>0.00029643804174372696</v>
+        <v>0.00029643804174372702</v>
       </c>
       <c r="J8">
         <v>0</v>
@@ -17394,11 +22434,11 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="305" t="s">
+      <c r="A9" s="641" t="s">
         <v>72</v>
       </c>
-      <c r="B9" s="306">
-        <v>0.012381197720877452</v>
+      <c r="B9" s="642">
+        <v>0.012381197720877425</v>
       </c>
       <c r="C9">
         <v>0</v>
@@ -17422,7 +22462,7 @@
         <v>0</v>
       </c>
       <c r="J9">
-        <v>0.00039174332855836596</v>
+        <v>0.00039174332855836601</v>
       </c>
       <c r="K9">
         <v>0</v>
@@ -17435,10 +22475,10 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="307" t="s">
+      <c r="A10" s="643" t="s">
         <v>73</v>
       </c>
-      <c r="B10" s="308">
+      <c r="B10" s="644">
         <v>-0.97802916114538907</v>
       </c>
       <c r="C10">
@@ -17466,7 +22506,7 @@
         <v>0</v>
       </c>
       <c r="K10">
-        <v>0.0014707991979309647</v>
+        <v>0.001470799197930964</v>
       </c>
       <c r="L10">
         <v>0</v>
@@ -17476,11 +22516,11 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="309" t="s">
+      <c r="A11" s="645" t="s">
         <v>74</v>
       </c>
-      <c r="B11" s="310">
-        <v>0.10085759388898095</v>
+      <c r="B11" s="646">
+        <v>0.10085759388898112</v>
       </c>
       <c r="C11">
         <v>0</v>
@@ -17517,11 +22557,11 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="311" t="s">
+      <c r="A12" s="647" t="s">
         <v>75</v>
       </c>
-      <c r="B12" s="312">
-        <v>0.058275709729466878</v>
+      <c r="B12" s="648">
+        <v>0.058275709729467114</v>
       </c>
       <c r="C12">
         <v>0</v>
@@ -17554,7 +22594,7 @@
         <v>0</v>
       </c>
       <c r="M12">
-        <v>0.00096483407043896924</v>
+        <v>0.00096483407043896946</v>
       </c>
     </row>
   </sheetData>
@@ -17567,10 +22607,10 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="313" t="s">
+      <c r="A1" s="649" t="s">
         <v>32</v>
       </c>
-      <c r="B1" s="314" t="s">
+      <c r="B1" s="650" t="s">
         <v>64</v>
       </c>
       <c r="C1" t="s">
@@ -17608,14 +22648,14 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="315" t="s">
+      <c r="A2" s="651" t="s">
         <v>65</v>
       </c>
-      <c r="B2" s="316">
-        <v>-0.52004949490141272</v>
+      <c r="B2" s="652">
+        <v>-0.52004949490141261</v>
       </c>
       <c r="C2">
-        <v>0.004991516270621674</v>
+        <v>0.0049915162706216766</v>
       </c>
       <c r="D2">
         <v>0</v>
@@ -17649,17 +22689,17 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="317" t="s">
+      <c r="A3" s="653" t="s">
         <v>66</v>
       </c>
-      <c r="B3" s="318">
-        <v>-0.13009282002310585</v>
+      <c r="B3" s="654">
+        <v>-0.13009282002310571</v>
       </c>
       <c r="C3">
         <v>0</v>
       </c>
       <c r="D3">
-        <v>0.0058574148876934179</v>
+        <v>0.0058574148876934197</v>
       </c>
       <c r="E3">
         <v>0</v>
@@ -17690,11 +22730,11 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="319" t="s">
+      <c r="A4" s="655" t="s">
         <v>67</v>
       </c>
-      <c r="B4" s="320">
-        <v>-0.76285415627959918</v>
+      <c r="B4" s="656">
+        <v>-0.76285415627959896</v>
       </c>
       <c r="C4">
         <v>0</v>
@@ -17703,7 +22743,7 @@
         <v>0</v>
       </c>
       <c r="E4">
-        <v>0.009086512805387869</v>
+        <v>0.0090865128053878759</v>
       </c>
       <c r="F4">
         <v>0</v>
@@ -17731,11 +22771,11 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="321" t="s">
+      <c r="A5" s="657" t="s">
         <v>68</v>
       </c>
-      <c r="B5" s="322">
-        <v>-0.035786085949105609</v>
+      <c r="B5" s="658">
+        <v>-0.035786085949105581</v>
       </c>
       <c r="C5">
         <v>0</v>
@@ -17747,7 +22787,7 @@
         <v>0</v>
       </c>
       <c r="F5">
-        <v>0.0020974101549432996</v>
+        <v>0.0020974101549432987</v>
       </c>
       <c r="G5">
         <v>0</v>
@@ -17772,11 +22812,11 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="323" t="s">
+      <c r="A6" s="659" t="s">
         <v>69</v>
       </c>
-      <c r="B6" s="324">
-        <v>-0.012497298626840382</v>
+      <c r="B6" s="660">
+        <v>-0.012497298626840318</v>
       </c>
       <c r="C6">
         <v>0</v>
@@ -17791,7 +22831,7 @@
         <v>0</v>
       </c>
       <c r="G6">
-        <v>0.0021186965778607794</v>
+        <v>0.0021186965778607803</v>
       </c>
       <c r="H6">
         <v>0</v>
@@ -17813,11 +22853,11 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="325" t="s">
+      <c r="A7" s="661" t="s">
         <v>70</v>
       </c>
-      <c r="B7" s="326">
-        <v>0.11354571776336225</v>
+      <c r="B7" s="662">
+        <v>0.11354571776336232</v>
       </c>
       <c r="C7">
         <v>0</v>
@@ -17835,7 +22875,7 @@
         <v>0</v>
       </c>
       <c r="H7">
-        <v>0.0034679217000289338</v>
+        <v>0.0034679217000289329</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -17854,11 +22894,11 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="327" t="s">
+      <c r="A8" s="663" t="s">
         <v>71</v>
       </c>
-      <c r="B8" s="328">
-        <v>-0.067340839259166382</v>
+      <c r="B8" s="664">
+        <v>-0.06734083925916641</v>
       </c>
       <c r="C8">
         <v>0</v>
@@ -17879,7 +22919,7 @@
         <v>0</v>
       </c>
       <c r="I8">
-        <v>0.00030051940437689467</v>
+        <v>0.00030051940437689478</v>
       </c>
       <c r="J8">
         <v>0</v>
@@ -17895,11 +22935,11 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="329" t="s">
+      <c r="A9" s="665" t="s">
         <v>72</v>
       </c>
-      <c r="B9" s="330">
-        <v>-0.014757928387821473</v>
+      <c r="B9" s="666">
+        <v>-0.01475792838782141</v>
       </c>
       <c r="C9">
         <v>0</v>
@@ -17923,7 +22963,7 @@
         <v>0</v>
       </c>
       <c r="J9">
-        <v>0.0003928115395695439</v>
+        <v>0.00039281153956954379</v>
       </c>
       <c r="K9">
         <v>0</v>
@@ -17936,11 +22976,11 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="331" t="s">
+      <c r="A10" s="667" t="s">
         <v>73</v>
       </c>
-      <c r="B10" s="332">
-        <v>-0.97078369051805691</v>
+      <c r="B10" s="668">
+        <v>-0.9707836905180568</v>
       </c>
       <c r="C10">
         <v>0</v>
@@ -17967,7 +23007,7 @@
         <v>0</v>
       </c>
       <c r="K10">
-        <v>0.0022555700579099816</v>
+        <v>0.0022555700579099812</v>
       </c>
       <c r="L10">
         <v>0</v>
@@ -17977,11 +23017,11 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="333" t="s">
+      <c r="A11" s="669" t="s">
         <v>74</v>
       </c>
-      <c r="B11" s="334">
-        <v>0.12055477704246831</v>
+      <c r="B11" s="670">
+        <v>0.12055477704246824</v>
       </c>
       <c r="C11">
         <v>0</v>
@@ -18011,18 +23051,18 @@
         <v>0</v>
       </c>
       <c r="L11">
-        <v>0.00087120443444414308</v>
+        <v>0.00087120443444414319</v>
       </c>
       <c r="M11">
         <v>0</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="335" t="s">
+      <c r="A12" s="671" t="s">
         <v>75</v>
       </c>
-      <c r="B12" s="336">
-        <v>0.1047782062348678</v>
+      <c r="B12" s="672">
+        <v>0.10477820623486774</v>
       </c>
       <c r="C12">
         <v>0</v>
